--- a/dcf/CFLT.xlsx
+++ b/dcf/CFLT.xlsx
@@ -879,7 +879,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>

--- a/dcf/CFLT.xlsx
+++ b/dcf/CFLT.xlsx
@@ -411,7 +411,7 @@
     </comment>
     <comment ref="B30" authorId="0" shapeId="0">
       <text>
-        <t>Opus: 22.0%</t>
+        <t>User-edited — overridden from Opus 22.0%</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0" shapeId="0">
@@ -432,22 +432,22 @@
     </comment>
     <comment ref="B38" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B39" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B40" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B41" authorId="0" shapeId="0">
       <text>
-        <t>builder default</t>
+        <t>workbook (synced) — no Opus pass — value synced from this workbook</t>
       </text>
     </comment>
     <comment ref="B43" authorId="0" shapeId="0">
@@ -1161,25 +1161,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>12.58247920302645</v>
+        <v>17.58231766830813</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>12.03487867817454</v>
+        <v>16.90707078476555</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>11.51575916079956</v>
+        <v>16.26492083347818</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>11.02355149313224</v>
+        <v>15.65409670130891</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>10.55677906992721</v>
+        <v>15.07292993905351</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>10.11405200284364</v>
+        <v>14.51984836262984</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>9.694061676761656</v>
+        <v>13.99337008050604</v>
       </c>
     </row>
     <row r="6">
@@ -1187,25 +1187,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>16.84444074546783</v>
+        <v>21.84427921074952</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>16.10201971815645</v>
+        <v>20.97421182474747</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>15.39783105484373</v>
+        <v>20.14699272752234</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>14.72977556145918</v>
+        <v>19.36032076963584</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>14.09587766629108</v>
+        <v>18.61202853541737</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>13.49427763184246</v>
+        <v>17.90007399162867</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>12.92322428950062</v>
+        <v>17.222532693245</v>
       </c>
     </row>
     <row r="7">
@@ -1213,25 +1213,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>21.10640228790921</v>
+        <v>26.1062407531909</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>20.16916075813837</v>
+        <v>25.04135286472939</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>19.27990294888789</v>
+        <v>24.0290646215665</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>18.43599962978611</v>
+        <v>23.06654483796278</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>17.63497626265494</v>
+        <v>22.15112713178124</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>16.87450326084129</v>
+        <v>21.2802996206275</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>16.15238690223958</v>
+        <v>20.45169530598396</v>
       </c>
     </row>
     <row r="8">
@@ -1239,51 +1239,51 @@
         <v>6</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>25.36836383035059</v>
+        <v>30.36820229563227</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>24.23630179812028</v>
+        <v>29.1084939047113</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>23.16197484293205</v>
+        <v>27.91113651561066</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>22.14222369811305</v>
+        <v>26.77276890628971</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>21.17407485901881</v>
+        <v>25.69022572814511</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>20.25472888984012</v>
+        <v>24.66052524962632</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>19.38154951497853</v>
+        <v>23.68085791872292</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="53" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="54" t="n">
-        <v>29.63032537279198</v>
-      </c>
-      <c r="C9" s="54" t="n">
-        <v>28.3034428381022</v>
-      </c>
-      <c r="D9" s="54" t="n">
-        <v>27.04404673697622</v>
+      <c r="B9" s="8" t="n">
+        <v>34.63016383807366</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>33.17563494469321</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>31.79320840965483</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>25.84844776643999</v>
+        <v>30.47899297461665</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>24.71317345538268</v>
+        <v>29.22932432450898</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>23.63495451883895</v>
+        <v>28.04075087862515</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>22.6107121277175</v>
+        <v>26.91002053146188</v>
       </c>
     </row>
     <row r="10">
@@ -1291,25 +1291,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>33.89228691523336</v>
+        <v>38.89212538051503</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>32.37058387808411</v>
-      </c>
-      <c r="D10" s="54" t="n">
-        <v>30.92611863102038</v>
-      </c>
-      <c r="E10" s="54" t="n">
-        <v>29.55467183476692</v>
-      </c>
-      <c r="F10" s="54" t="n">
-        <v>28.25227205174654</v>
-      </c>
-      <c r="G10" s="54" t="n">
-        <v>27.01518014783777</v>
+        <v>37.24277598467513</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>35.67528030369899</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>34.18521704294358</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>32.76842292087284</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>31.42097650762398</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>25.83987474045646</v>
+        <v>30.13918314420084</v>
       </c>
     </row>
     <row r="11">
@@ -1317,25 +1317,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>38.15424845767474</v>
+        <v>43.15408692295642</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>36.43772491806603</v>
+        <v>41.30991702465705</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>34.80819052506454</v>
+        <v>39.55735219774315</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>33.26089590309386</v>
+        <v>37.89144111127052</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>31.79137064811041</v>
-      </c>
-      <c r="G11" s="54" t="n">
-        <v>30.3954057768366</v>
-      </c>
-      <c r="H11" s="54" t="n">
-        <v>29.06903735319543</v>
+        <v>36.30752151723672</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>34.80120213662281</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>33.3683457569398</v>
       </c>
     </row>
     <row r="13">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>2.791348176711717</v>
+        <v>2.952608914307358</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24293,7 +24293,7 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -24650,13 +24650,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>22.14222369811305</v>
+        <v>26.77276890628971</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>34.85792662374777</v>
+        <v>39.96385900479662</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>12.26588088829715</v>
+        <v>16.46362503583224</v>
       </c>
     </row>
     <row r="59">
@@ -24726,7 +24726,7 @@
         </is>
       </c>
       <c r="B65" s="15" t="n">
-        <v>0.3405405451734222</v>
+        <v>0.2</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         </is>
       </c>
       <c r="B66" s="15" t="n">
-        <v>0.2043243271040533</v>
+        <v>0.1</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -25167,9 +25167,9 @@
         <f>Dashboard!B30</f>
         <v/>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Opus</t>
+      <c r="D29" s="32" t="inlineStr">
+        <is>
+          <t>user-edited</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -25177,7 +25177,11 @@
           <t>22.0%</t>
         </is>
       </c>
-      <c r="F29" s="31" t="inlineStr"/>
+      <c r="F29" s="31" t="inlineStr">
+        <is>
+          <t>overridden from Opus 22.0%</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -25254,7 +25258,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -25262,7 +25266,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="31" t="inlineStr"/>
+      <c r="F32" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -25281,7 +25289,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -25289,7 +25297,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F33" s="31" t="inlineStr"/>
+      <c r="F33" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -25308,7 +25320,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -25316,7 +25328,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F34" s="31" t="inlineStr"/>
+      <c r="F34" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -25335,7 +25351,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>builder default</t>
+          <t>workbook (synced)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -25343,7 +25359,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="31" t="inlineStr"/>
+      <c r="F35" s="31" t="inlineStr">
+        <is>
+          <t>no Opus pass — value synced from this workbook</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
